--- a/plantilla_importacion_imei.xlsx
+++ b/plantilla_importacion_imei.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
   <si>
     <t>MODELO</t>
   </si>
@@ -32,6 +32,9 @@
     <t>N_FACTURA</t>
   </si>
   <si>
+    <t>CATEGORIA</t>
+  </si>
+  <si>
     <t>GALAXY A15 128GB</t>
   </si>
   <si>
@@ -53,6 +56,12 @@
     <t>F001-000123</t>
   </si>
   <si>
+    <t>MOVIL</t>
+  </si>
+  <si>
+    <t>IFI</t>
+  </si>
+  <si>
     <t>INSTRUCCIONES DE IMPORTACIÓN</t>
   </si>
   <si>
@@ -69,6 +78,9 @@
   </si>
   <si>
     <t>5. La fecha de compra y el tipo (EQUIPO / SIM) se eligen en el sistema al importar.</t>
+  </si>
+  <si>
+    <t>5b. CATEGORIA (opcional): MOVIL, IFI, TFI u OLO. Si se deja vacía se usa la categoría elegida en pantalla.</t>
   </si>
   <si>
     <t>6. El sistema rechaza IMEI duplicados, con longitud incorrecta o dígito verificador inválido.</t>
@@ -110,7 +122,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDA291C"/>
+        <fgColor rgb="FF0B1E3F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,7 +452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
@@ -448,9 +460,10 @@
     <col min="3" max="3" width="22.7109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="12.7109375" customWidth="1"/>
     <col min="5" max="5" width="16.7109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -466,49 +479,63 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2">
         <v>599</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="D3">
         <v>529</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F20001">
+      <formula1>"MOVIL,IFI,TFI,OLO"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="110.7109375" customWidth="1"/>
@@ -516,42 +543,47 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
